--- a/software-quote-builder/assets/standard-quote-template.xlsx
+++ b/software-quote-builder/assets/standard-quote-template.xlsx
@@ -163,14 +163,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="5" max="5" width="48" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
@@ -256,11 +256,43 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">特殊说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 仅为软件功能开发费用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. 默认包含自项目验收之日起一年的维护期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. 服务器及第三方服务相关费用由客户自行支付。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:I2"/>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
